--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/43.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/43.xlsx
@@ -426,13 +426,13 @@
         <v>-19.94980508631523</v>
       </c>
       <c r="E2">
-        <v>-15.33496380479006</v>
+        <v>-21.66674408942486</v>
       </c>
       <c r="F2">
-        <v>1.619592838306934</v>
+        <v>0.06687371280897446</v>
       </c>
       <c r="G2">
-        <v>-11.76656722344266</v>
+        <v>-15.77193668158716</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.41350078965078</v>
       </c>
       <c r="E3">
-        <v>-16.03995210983017</v>
+        <v>-21.18503219533294</v>
       </c>
       <c r="F3">
-        <v>1.647561084773594</v>
+        <v>0.1179878212297826</v>
       </c>
       <c r="G3">
-        <v>-11.70608024589463</v>
+        <v>-16.09443182002249</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.82435230643546</v>
       </c>
       <c r="E4">
-        <v>-14.47305934691016</v>
+        <v>-19.83759381129864</v>
       </c>
       <c r="F4">
-        <v>2.211841837268331</v>
+        <v>0.8845141539497987</v>
       </c>
       <c r="G4">
-        <v>-11.8092434659894</v>
+        <v>-14.47065558064753</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.22890116248765</v>
       </c>
       <c r="E5">
-        <v>-15.92114306576493</v>
+        <v>-24.27563419303582</v>
       </c>
       <c r="F5">
-        <v>1.845619346558452</v>
+        <v>0.3185451709492034</v>
       </c>
       <c r="G5">
-        <v>-10.81851305517941</v>
+        <v>-14.56982131700362</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.63403475200703</v>
       </c>
       <c r="E6">
-        <v>-15.81622737995522</v>
+        <v>-22.45972064443401</v>
       </c>
       <c r="F6">
-        <v>2.039420606842608</v>
+        <v>-0.01001204197377984</v>
       </c>
       <c r="G6">
-        <v>-11.08540592600991</v>
+        <v>-14.76928168574471</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.05435514512919</v>
       </c>
       <c r="E7">
-        <v>-17.01605109676149</v>
+        <v>-21.92828610573786</v>
       </c>
       <c r="F7">
-        <v>2.125540950818289</v>
+        <v>1.084886210077113</v>
       </c>
       <c r="G7">
-        <v>-10.68671361616995</v>
+        <v>-15.69178175299032</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.47971055852306</v>
       </c>
       <c r="E8">
-        <v>-18.25703864229748</v>
+        <v>-21.74149560986948</v>
       </c>
       <c r="F8">
-        <v>2.17918582129197</v>
+        <v>-0.1274739260160082</v>
       </c>
       <c r="G8">
-        <v>-10.38851953726563</v>
+        <v>-15.55332480690139</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.92854255056001</v>
       </c>
       <c r="E9">
-        <v>-18.87397982720646</v>
+        <v>-23.60008096904556</v>
       </c>
       <c r="F9">
-        <v>2.164270478980361</v>
+        <v>1.454211180675338</v>
       </c>
       <c r="G9">
-        <v>-11.211272867413</v>
+        <v>-14.94471411496177</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.3976118781426</v>
       </c>
       <c r="E10">
-        <v>-19.3450679212764</v>
+        <v>-23.89997916020353</v>
       </c>
       <c r="F10">
-        <v>2.094031537924706</v>
+        <v>0.3403448828752274</v>
       </c>
       <c r="G10">
-        <v>-11.20353612248773</v>
+        <v>-14.84098148103425</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.88168921007084</v>
       </c>
       <c r="E11">
-        <v>-19.59870775044601</v>
+        <v>-23.24044767725241</v>
       </c>
       <c r="F11">
-        <v>2.662669065392817</v>
+        <v>0.579967506410793</v>
       </c>
       <c r="G11">
-        <v>-9.100565037394334</v>
+        <v>-13.7856176343883</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.37285011425065</v>
       </c>
       <c r="E12">
-        <v>-20.26463796716997</v>
+        <v>-27.11642292210556</v>
       </c>
       <c r="F12">
-        <v>2.693565584097125</v>
+        <v>1.101372588656838</v>
       </c>
       <c r="G12">
-        <v>-8.356970161636477</v>
+        <v>-13.38292453026412</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.852565281546</v>
       </c>
       <c r="E13">
-        <v>-20.26396775301683</v>
+        <v>-23.87741377422331</v>
       </c>
       <c r="F13">
-        <v>2.708370066994653</v>
+        <v>0.3191636081091825</v>
       </c>
       <c r="G13">
-        <v>-8.649446928394468</v>
+        <v>-13.39892439685542</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.32943937166908</v>
       </c>
       <c r="E14">
-        <v>-20.33655919135979</v>
+        <v>-26.48019496639792</v>
       </c>
       <c r="F14">
-        <v>2.377318517254853</v>
+        <v>0.8094464935579689</v>
       </c>
       <c r="G14">
-        <v>-8.197567393920568</v>
+        <v>-12.52771130110419</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.79883126323735</v>
       </c>
       <c r="E15">
-        <v>-22.29418227708362</v>
+        <v>-27.02240727323232</v>
       </c>
       <c r="F15">
-        <v>3.27622049262279</v>
+        <v>2.040573544749047</v>
       </c>
       <c r="G15">
-        <v>-7.396418683962481</v>
+        <v>-11.57735299314561</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.25574823225623</v>
       </c>
       <c r="E16">
-        <v>-23.89218112796232</v>
+        <v>-27.93999384751053</v>
       </c>
       <c r="F16">
-        <v>3.45671703951134</v>
+        <v>1.913816890689105</v>
       </c>
       <c r="G16">
-        <v>-7.799255796817617</v>
+        <v>-13.00410873584193</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.69659024470919</v>
       </c>
       <c r="E17">
-        <v>-23.69004363368194</v>
+        <v>-27.7936199821606</v>
       </c>
       <c r="F17">
-        <v>3.89741646830659</v>
+        <v>1.476449579139939</v>
       </c>
       <c r="G17">
-        <v>-7.704173618384209</v>
+        <v>-12.05233351439255</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.11189132103218</v>
       </c>
       <c r="E18">
-        <v>-24.14492884775243</v>
+        <v>-31.20954981681153</v>
       </c>
       <c r="F18">
-        <v>3.577327330913462</v>
+        <v>1.563472635487421</v>
       </c>
       <c r="G18">
-        <v>-6.383666524225257</v>
+        <v>-12.12871442107461</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.51598018088433</v>
       </c>
       <c r="E19">
-        <v>-26.57090935771957</v>
+        <v>-30.79378608969331</v>
       </c>
       <c r="F19">
-        <v>3.940315894144014</v>
+        <v>2.327799200690892</v>
       </c>
       <c r="G19">
-        <v>-5.717776773365172</v>
+        <v>-10.50663318101575</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.915531449303124</v>
       </c>
       <c r="E20">
-        <v>-26.40795222055355</v>
+        <v>-31.64053148083253</v>
       </c>
       <c r="F20">
-        <v>4.241665039439748</v>
+        <v>2.194851840207497</v>
       </c>
       <c r="G20">
-        <v>-5.445494334396734</v>
+        <v>-11.09001089485504</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.317650057534435</v>
       </c>
       <c r="E21">
-        <v>-27.13630745147324</v>
+        <v>-32.16906326768976</v>
       </c>
       <c r="F21">
-        <v>4.268578537766725</v>
+        <v>2.633801273966187</v>
       </c>
       <c r="G21">
-        <v>-5.892954290575707</v>
+        <v>-10.4594380438079</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.730529847246281</v>
       </c>
       <c r="E22">
-        <v>-28.70689092070951</v>
+        <v>-32.84014915207145</v>
       </c>
       <c r="F22">
-        <v>4.193236896251524</v>
+        <v>2.723176133598097</v>
       </c>
       <c r="G22">
-        <v>-5.032606405284372</v>
+        <v>-9.389317440420646</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.156347008319736</v>
       </c>
       <c r="E23">
-        <v>-28.47248804912448</v>
+        <v>-32.90000652150484</v>
       </c>
       <c r="F23">
-        <v>4.201959948433765</v>
+        <v>2.682690275575802</v>
       </c>
       <c r="G23">
-        <v>-4.552686550092846</v>
+        <v>-9.342009744664461</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.614294915423996</v>
       </c>
       <c r="E24">
-        <v>-29.15838430774825</v>
+        <v>-33.73340423550645</v>
       </c>
       <c r="F24">
-        <v>4.273901373348517</v>
+        <v>2.560966638915127</v>
       </c>
       <c r="G24">
-        <v>-3.908378245603269</v>
+        <v>-8.877702422236137</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.117056172005443</v>
       </c>
       <c r="E25">
-        <v>-29.10139799083573</v>
+        <v>-34.94063427155226</v>
       </c>
       <c r="F25">
-        <v>3.943644843978268</v>
+        <v>3.544623803759637</v>
       </c>
       <c r="G25">
-        <v>-3.607628425542639</v>
+        <v>-10.4766263962478</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.674717441302234</v>
       </c>
       <c r="E26">
-        <v>-28.54204088140828</v>
+        <v>-34.74910246339785</v>
       </c>
       <c r="F26">
-        <v>3.990053762124305</v>
+        <v>2.637073210387485</v>
       </c>
       <c r="G26">
-        <v>-3.465288209536135</v>
+        <v>-9.267827040220473</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.295840557947586</v>
       </c>
       <c r="E27">
-        <v>-30.62406567659683</v>
+        <v>-34.1535515254641</v>
       </c>
       <c r="F27">
-        <v>4.57508422952313</v>
+        <v>2.873511001327101</v>
       </c>
       <c r="G27">
-        <v>-2.827081240475435</v>
+        <v>-8.61337191365303</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.980605692347947</v>
       </c>
       <c r="E28">
-        <v>-30.22301269729252</v>
+        <v>-34.9141449628444</v>
       </c>
       <c r="F28">
-        <v>4.236728628101322</v>
+        <v>2.651063668444477</v>
       </c>
       <c r="G28">
-        <v>-4.159443398210517</v>
+        <v>-9.053386452914181</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.738526520143274</v>
       </c>
       <c r="E29">
-        <v>-29.95168917712295</v>
+        <v>-35.13826593419501</v>
       </c>
       <c r="F29">
-        <v>4.208454726392982</v>
+        <v>2.87049720897002</v>
       </c>
       <c r="G29">
-        <v>-3.198027868150772</v>
+        <v>-8.073690090386581</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.571365954718933</v>
       </c>
       <c r="E30">
-        <v>-30.19946463245264</v>
+        <v>-36.81812600971037</v>
       </c>
       <c r="F30">
-        <v>4.04481514526837</v>
+        <v>2.459139099670116</v>
       </c>
       <c r="G30">
-        <v>-3.636824126653472</v>
+        <v>-7.171400903658218</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.475361674659307</v>
       </c>
       <c r="E31">
-        <v>-29.34712657591394</v>
+        <v>-35.35507115578624</v>
       </c>
       <c r="F31">
-        <v>4.244943310684707</v>
+        <v>2.692297035658858</v>
       </c>
       <c r="G31">
-        <v>-2.948187617393054</v>
+        <v>-8.06283150101777</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.4444756798553</v>
       </c>
       <c r="E32">
-        <v>-28.97433353865451</v>
+        <v>-35.05624168449408</v>
       </c>
       <c r="F32">
-        <v>3.814734349873328</v>
+        <v>1.971354510302936</v>
       </c>
       <c r="G32">
-        <v>-4.110801552602005</v>
+        <v>-9.192151279738273</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.466218141589867</v>
       </c>
       <c r="E33">
-        <v>-29.76838787047748</v>
+        <v>-33.22138552911819</v>
       </c>
       <c r="F33">
-        <v>4.023756607710772</v>
+        <v>2.349652758618041</v>
       </c>
       <c r="G33">
-        <v>-2.768795775711027</v>
+        <v>-8.562866230905909</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.53640701925161</v>
       </c>
       <c r="E34">
-        <v>-28.60469684777841</v>
+        <v>-34.38050958578052</v>
       </c>
       <c r="F34">
-        <v>4.352717665642192</v>
+        <v>2.259167721139408</v>
       </c>
       <c r="G34">
-        <v>-3.34666474177297</v>
+        <v>-8.027878761214145</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.649861626115351</v>
       </c>
       <c r="E35">
-        <v>-29.50429632329816</v>
+        <v>-32.89371420687117</v>
       </c>
       <c r="F35">
-        <v>4.281268773267142</v>
+        <v>2.862640443923525</v>
       </c>
       <c r="G35">
-        <v>-3.374595814487801</v>
+        <v>-8.581345696106121</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.799385897777372</v>
       </c>
       <c r="E36">
-        <v>-27.80202482991884</v>
+        <v>-36.21274149046896</v>
       </c>
       <c r="F36">
-        <v>4.276264262574353</v>
+        <v>1.821358555639835</v>
       </c>
       <c r="G36">
-        <v>-3.786268773387251</v>
+        <v>-8.572761451522791</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.978585759209782</v>
       </c>
       <c r="E37">
-        <v>-26.64030369341311</v>
+        <v>-33.5256763400636</v>
       </c>
       <c r="F37">
-        <v>4.404150098952003</v>
+        <v>1.719603866866935</v>
       </c>
       <c r="G37">
-        <v>-3.477427980028642</v>
+        <v>-7.959966230021537</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.177312872680373</v>
       </c>
       <c r="E38">
-        <v>-28.09503068363714</v>
+        <v>-32.52399147498894</v>
       </c>
       <c r="F38">
-        <v>4.097332417130258</v>
+        <v>2.259577900971507</v>
       </c>
       <c r="G38">
-        <v>-4.653522456673507</v>
+        <v>-10.5679908320406</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.392803902647377</v>
       </c>
       <c r="E39">
-        <v>-26.69911045687672</v>
+        <v>-31.45602333586401</v>
       </c>
       <c r="F39">
-        <v>4.477372741952347</v>
+        <v>2.313094491266037</v>
       </c>
       <c r="G39">
-        <v>-4.938795476338043</v>
+        <v>-9.022065381567137</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.624860156763708</v>
       </c>
       <c r="E40">
-        <v>-25.65372128915403</v>
+        <v>-31.16816182861842</v>
       </c>
       <c r="F40">
-        <v>4.41127360815965</v>
+        <v>3.018431178531219</v>
       </c>
       <c r="G40">
-        <v>-4.490044407398756</v>
+        <v>-8.450003112381076</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.871674620166559</v>
       </c>
       <c r="E41">
-        <v>-26.94152419898132</v>
+        <v>-32.04074216397141</v>
       </c>
       <c r="F41">
-        <v>4.433660874980302</v>
+        <v>2.604985744834766</v>
       </c>
       <c r="G41">
-        <v>-5.040356392391805</v>
+        <v>-9.65816684366486</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.132243747364654</v>
       </c>
       <c r="E42">
-        <v>-25.49478090843282</v>
+        <v>-31.60674000778729</v>
       </c>
       <c r="F42">
-        <v>4.615170993654733</v>
+        <v>2.338775866390803</v>
       </c>
       <c r="G42">
-        <v>-5.090322456216025</v>
+        <v>-10.14474420593586</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.401666700527239</v>
       </c>
       <c r="E43">
-        <v>-24.91909865020772</v>
+        <v>-30.8150359539743</v>
       </c>
       <c r="F43">
-        <v>5.359883361095486</v>
+        <v>3.18424835528956</v>
       </c>
       <c r="G43">
-        <v>-5.760366941727896</v>
+        <v>-9.698423077422397</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.680571858464117</v>
       </c>
       <c r="E44">
-        <v>-24.69620263107618</v>
+        <v>-30.28688682317071</v>
       </c>
       <c r="F44">
-        <v>4.663022667889736</v>
+        <v>3.059577441920251</v>
       </c>
       <c r="G44">
-        <v>-5.919971652721699</v>
+        <v>-9.379163997251702</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.973366659790718</v>
       </c>
       <c r="E45">
-        <v>-24.04694625564846</v>
+        <v>-28.05059729667387</v>
       </c>
       <c r="F45">
-        <v>5.244271245562491</v>
+        <v>3.413519876961813</v>
       </c>
       <c r="G45">
-        <v>-5.628339075076221</v>
+        <v>-9.280132337989944</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.28099268142512</v>
       </c>
       <c r="E46">
-        <v>-23.25416895349565</v>
+        <v>-28.30813161349009</v>
       </c>
       <c r="F46">
-        <v>5.071476260540724</v>
+        <v>3.582046774541471</v>
       </c>
       <c r="G46">
-        <v>-6.538427907095106</v>
+        <v>-8.767782378695717</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.603936834637631</v>
       </c>
       <c r="E47">
-        <v>-23.60928282822915</v>
+        <v>-29.06364863150779</v>
       </c>
       <c r="F47">
-        <v>5.15685543014798</v>
+        <v>3.436665738915961</v>
       </c>
       <c r="G47">
-        <v>-5.702107961327801</v>
+        <v>-11.95980376656992</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.936818276819098</v>
       </c>
       <c r="E48">
-        <v>-21.33525979206339</v>
+        <v>-25.22371098280768</v>
       </c>
       <c r="F48">
-        <v>5.368478133098576</v>
+        <v>3.311367678004138</v>
       </c>
       <c r="G48">
-        <v>-6.065082795344573</v>
+        <v>-10.42621009823024</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.277222036962423</v>
       </c>
       <c r="E49">
-        <v>-21.78219753425042</v>
+        <v>-26.42677708700344</v>
       </c>
       <c r="F49">
-        <v>5.018876635971234</v>
+        <v>2.961664823698207</v>
       </c>
       <c r="G49">
-        <v>-5.4614577849871</v>
+        <v>-10.61160064842942</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.627254668087188</v>
       </c>
       <c r="E50">
-        <v>-22.1280914359043</v>
+        <v>-24.66347987789675</v>
       </c>
       <c r="F50">
-        <v>5.218995299152078</v>
+        <v>3.380068840615901</v>
       </c>
       <c r="G50">
-        <v>-5.305349010082767</v>
+        <v>-11.4717664537161</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.984065776257605</v>
       </c>
       <c r="E51">
-        <v>-18.9323926134314</v>
+        <v>-26.40052099470697</v>
       </c>
       <c r="F51">
-        <v>5.50590579761675</v>
+        <v>3.096865797699273</v>
       </c>
       <c r="G51">
-        <v>-6.292788738626724</v>
+        <v>-11.63015950504253</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.34367267917362</v>
       </c>
       <c r="E52">
-        <v>-20.21967927722182</v>
+        <v>-25.66739275218319</v>
       </c>
       <c r="F52">
-        <v>5.560122385925903</v>
+        <v>4.100317702780861</v>
       </c>
       <c r="G52">
-        <v>-6.587887457451818</v>
+        <v>-13.07077981245732</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.69633548223679</v>
       </c>
       <c r="E53">
-        <v>-18.87344999574757</v>
+        <v>-26.90389710845159</v>
       </c>
       <c r="F53">
-        <v>5.64490766581487</v>
+        <v>4.099628790707645</v>
       </c>
       <c r="G53">
-        <v>-7.422932843186504</v>
+        <v>-12.10965561040503</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.0353906515586</v>
       </c>
       <c r="E54">
-        <v>-20.70349691172731</v>
+        <v>-26.1418364454928</v>
       </c>
       <c r="F54">
-        <v>5.527551890068976</v>
+        <v>3.269065309296835</v>
       </c>
       <c r="G54">
-        <v>-7.063116269614197</v>
+        <v>-11.20799542732913</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.3617973399646</v>
       </c>
       <c r="E55">
-        <v>-19.48526494807986</v>
+        <v>-25.2739679873448</v>
       </c>
       <c r="F55">
-        <v>5.807829828159788</v>
+        <v>3.448543533281757</v>
       </c>
       <c r="G55">
-        <v>-7.226365891246738</v>
+        <v>-11.49930357151175</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.67171046728548</v>
       </c>
       <c r="E56">
-        <v>-18.16458531695688</v>
+        <v>-23.08000384316065</v>
       </c>
       <c r="F56">
-        <v>5.406308116300679</v>
+        <v>3.949442791334691</v>
       </c>
       <c r="G56">
-        <v>-6.480096094693148</v>
+        <v>-11.52288458738798</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.9612975775642</v>
       </c>
       <c r="E57">
-        <v>-17.82430672307252</v>
+        <v>-22.60862592675423</v>
       </c>
       <c r="F57">
-        <v>5.506298556683778</v>
+        <v>3.830813716032784</v>
       </c>
       <c r="G57">
-        <v>-7.82754109790515</v>
+        <v>-12.25187333622658</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.22228448574346</v>
       </c>
       <c r="E58">
-        <v>-17.34521681543103</v>
+        <v>-21.02817944112926</v>
       </c>
       <c r="F58">
-        <v>5.047160039915067</v>
+        <v>3.365920011967365</v>
       </c>
       <c r="G58">
-        <v>-7.075693032117888</v>
+        <v>-12.74126135166042</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.44992929872115</v>
       </c>
       <c r="E59">
-        <v>-17.32072682799755</v>
+        <v>-21.94490107687201</v>
       </c>
       <c r="F59">
-        <v>5.198411873369111</v>
+        <v>3.200201024975782</v>
       </c>
       <c r="G59">
-        <v>-6.939262139898983</v>
+        <v>-11.13833492809178</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.64993266265266</v>
       </c>
       <c r="E60">
-        <v>-17.39410169234383</v>
+        <v>-21.74355606554297</v>
       </c>
       <c r="F60">
-        <v>5.171492040218471</v>
+        <v>3.708192118118054</v>
       </c>
       <c r="G60">
-        <v>-6.434923700809793</v>
+        <v>-13.21174615206502</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.82248321689474</v>
       </c>
       <c r="E61">
-        <v>-15.96408205630566</v>
+        <v>-22.35809715922788</v>
       </c>
       <c r="F61">
-        <v>5.160551799754615</v>
+        <v>2.731732896659216</v>
       </c>
       <c r="G61">
-        <v>-7.293285258777566</v>
+        <v>-10.88006933893662</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.96774388092191</v>
       </c>
       <c r="E62">
-        <v>-16.00738785324101</v>
+        <v>-21.59892113421198</v>
       </c>
       <c r="F62">
-        <v>5.198302597660946</v>
+        <v>3.749987700932417</v>
       </c>
       <c r="G62">
-        <v>-7.88631983395491</v>
+        <v>-12.39762010359299</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.08146637622889</v>
       </c>
       <c r="E63">
-        <v>-15.2309628707299</v>
+        <v>-21.9465494414108</v>
       </c>
       <c r="F63">
-        <v>4.722961185671373</v>
+        <v>3.102703337703583</v>
       </c>
       <c r="G63">
-        <v>-7.805817298076452</v>
+        <v>-12.12790002687195</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.16131715636861</v>
       </c>
       <c r="E64">
-        <v>-15.31913225965924</v>
+        <v>-19.69206677058814</v>
       </c>
       <c r="F64">
-        <v>4.802876569870363</v>
+        <v>3.312986225449717</v>
       </c>
       <c r="G64">
-        <v>-7.924536771660256</v>
+        <v>-14.30006151373611</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.21603036009556</v>
       </c>
       <c r="E65">
-        <v>-14.80660409994512</v>
+        <v>-21.10069389541409</v>
       </c>
       <c r="F65">
-        <v>4.707382270581195</v>
+        <v>2.876686331687558</v>
       </c>
       <c r="G65">
-        <v>-7.031795198267152</v>
+        <v>-12.17631344483825</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.24718604373507</v>
       </c>
       <c r="E66">
-        <v>-14.89584220874027</v>
+        <v>-22.46688469031415</v>
       </c>
       <c r="F66">
-        <v>4.27263282491025</v>
+        <v>2.51014709979459</v>
       </c>
       <c r="G66">
-        <v>-7.87337560089636</v>
+        <v>-11.65748143737813</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.25610345692821</v>
       </c>
       <c r="E67">
-        <v>-15.22280708904208</v>
+        <v>-20.13962038524021</v>
       </c>
       <c r="F67">
-        <v>4.563784487816469</v>
+        <v>2.576829037364168</v>
       </c>
       <c r="G67">
-        <v>-6.42817018790968</v>
+        <v>-12.95888006268441</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.2392163194395</v>
       </c>
       <c r="E68">
-        <v>-14.73675691685081</v>
+        <v>-20.28240769917607</v>
       </c>
       <c r="F68">
-        <v>4.32330191196882</v>
+        <v>1.983449272379147</v>
       </c>
       <c r="G68">
-        <v>-7.426197041088225</v>
+        <v>-11.67332570832908</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.19405588912945</v>
       </c>
       <c r="E69">
-        <v>-14.34075092182805</v>
+        <v>-19.48886508491596</v>
       </c>
       <c r="F69">
-        <v>4.124713108702291</v>
+        <v>2.505999374002054</v>
       </c>
       <c r="G69">
-        <v>-6.87173032144339</v>
+        <v>-13.03710825377739</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.13009630508599</v>
       </c>
       <c r="E70">
-        <v>-15.36034137312904</v>
+        <v>-20.58045827293891</v>
       </c>
       <c r="F70">
-        <v>4.147315759527443</v>
+        <v>2.356698666235831</v>
       </c>
       <c r="G70">
-        <v>-7.845308795814418</v>
+        <v>-13.24946319739394</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.04865051726404</v>
       </c>
       <c r="E71">
-        <v>-13.84760463086676</v>
+        <v>-20.00791424720113</v>
       </c>
       <c r="F71">
-        <v>3.399714712496928</v>
+        <v>2.411684935619889</v>
       </c>
       <c r="G71">
-        <v>-7.283687987259218</v>
+        <v>-10.30555395550596</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.95057172480246</v>
       </c>
       <c r="E72">
-        <v>-14.49650325684787</v>
+        <v>-21.0842872340843</v>
       </c>
       <c r="F72">
-        <v>3.769799861934564</v>
+        <v>2.163152382604061</v>
       </c>
       <c r="G72">
-        <v>-7.38147488139821</v>
+        <v>-12.29177865215695</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.83288783003109</v>
       </c>
       <c r="E73">
-        <v>-14.60209821375872</v>
+        <v>-17.7186755383696</v>
       </c>
       <c r="F73">
-        <v>3.928832442551163</v>
+        <v>2.346084669190556</v>
       </c>
       <c r="G73">
-        <v>-6.814805490895623</v>
+        <v>-12.18112366750681</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.6925045528364</v>
       </c>
       <c r="E74">
-        <v>-14.7245889071922</v>
+        <v>-21.0157442515042</v>
       </c>
       <c r="F74">
-        <v>3.916465283057496</v>
+        <v>1.352690880377924</v>
       </c>
       <c r="G74">
-        <v>-6.986725431295514</v>
+        <v>-11.46835990235619</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.53973707875448</v>
       </c>
       <c r="E75">
-        <v>-14.67186388432089</v>
+        <v>-22.51545257404641</v>
       </c>
       <c r="F75">
-        <v>3.376956858492063</v>
+        <v>1.449992188116608</v>
       </c>
       <c r="G75">
-        <v>-6.62839860321588</v>
+        <v>-11.24730484506243</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.3767605871186</v>
       </c>
       <c r="E76">
-        <v>-14.43333557291487</v>
+        <v>-19.378488059453</v>
       </c>
       <c r="F76">
-        <v>3.709050486724222</v>
+        <v>1.862376538849716</v>
       </c>
       <c r="G76">
-        <v>-6.929025933091557</v>
+        <v>-10.98189178808798</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.20565627662579</v>
       </c>
       <c r="E77">
-        <v>-15.03018844712583</v>
+        <v>-20.01910863494809</v>
       </c>
       <c r="F77">
-        <v>3.480787785720104</v>
+        <v>1.607977939123101</v>
       </c>
       <c r="G77">
-        <v>-6.025293348508073</v>
+        <v>-9.543290913452148</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.02567498872134</v>
       </c>
       <c r="E78">
-        <v>-16.5666543931883</v>
+        <v>-22.41594841467587</v>
       </c>
       <c r="F78">
-        <v>3.36211595035848</v>
+        <v>1.316677407860831</v>
       </c>
       <c r="G78">
-        <v>-6.375731146567624</v>
+        <v>-11.09068293559951</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.83487980438123</v>
       </c>
       <c r="E79">
-        <v>-16.09125972033707</v>
+        <v>-21.81168242851436</v>
       </c>
       <c r="F79">
-        <v>3.703198693366673</v>
+        <v>2.266471772821415</v>
       </c>
       <c r="G79">
-        <v>-6.161005852344956</v>
+        <v>-10.17965390864747</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.64565054189144</v>
       </c>
       <c r="E80">
-        <v>-16.37644037097012</v>
+        <v>-21.22335214238585</v>
       </c>
       <c r="F80">
-        <v>3.527890367057104</v>
+        <v>1.309172225527563</v>
       </c>
       <c r="G80">
-        <v>-5.402553248206848</v>
+        <v>-10.49019632241327</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.46104369965985</v>
       </c>
       <c r="E81">
-        <v>-17.64739735748887</v>
+        <v>-22.87151742832152</v>
       </c>
       <c r="F81">
-        <v>3.352715072044431</v>
+        <v>1.286767537941841</v>
       </c>
       <c r="G81">
-        <v>-6.250532935363466</v>
+        <v>-9.453035510414999</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.28342569787525</v>
       </c>
       <c r="E82">
-        <v>-18.4765564198193</v>
+        <v>-22.00660153522652</v>
       </c>
       <c r="F82">
-        <v>3.408874867511829</v>
+        <v>1.776302122345582</v>
       </c>
       <c r="G82">
-        <v>-5.274375546017346</v>
+        <v>-9.224247018741506</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.11172665204795</v>
       </c>
       <c r="E83">
-        <v>-18.13535854571138</v>
+        <v>-23.01311375359336</v>
       </c>
       <c r="F83">
-        <v>3.18023049338209</v>
+        <v>1.601327957984171</v>
       </c>
       <c r="G83">
-        <v>-5.563449071960967</v>
+        <v>-8.552295658999016</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.94115256076773</v>
       </c>
       <c r="E84">
-        <v>-19.21431729125293</v>
+        <v>-24.55307568158975</v>
       </c>
       <c r="F84">
-        <v>3.291340132997491</v>
+        <v>1.250438907947576</v>
       </c>
       <c r="G84">
-        <v>-5.173311211794475</v>
+        <v>-8.011282996425779</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.78076557091729</v>
       </c>
       <c r="E85">
-        <v>-19.71192865758579</v>
+        <v>-25.94499273732739</v>
       </c>
       <c r="F85">
-        <v>2.892523390841952</v>
+        <v>1.111451293102694</v>
       </c>
       <c r="G85">
-        <v>-4.791479510386015</v>
+        <v>-8.136808951638324</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.62947882977513</v>
       </c>
       <c r="E86">
-        <v>-21.11977688488241</v>
+        <v>-28.66995668670295</v>
       </c>
       <c r="F86">
-        <v>3.179658775546617</v>
+        <v>1.915810776436643</v>
       </c>
       <c r="G86">
-        <v>-4.875087337980309</v>
+        <v>-9.079347751033145</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.48432124352788</v>
       </c>
       <c r="E87">
-        <v>-23.01285563057492</v>
+        <v>-26.34042361615117</v>
       </c>
       <c r="F87">
-        <v>3.258707872609861</v>
+        <v>1.660867381875117</v>
       </c>
       <c r="G87">
-        <v>-4.562359964158595</v>
+        <v>-7.780683636342305</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.33890598707807</v>
       </c>
       <c r="E88">
-        <v>-23.76718618840261</v>
+        <v>-28.80787136260655</v>
       </c>
       <c r="F88">
-        <v>3.057059349514703</v>
+        <v>1.793733973356824</v>
       </c>
       <c r="G88">
-        <v>-4.214719577079729</v>
+        <v>-9.217629238208504</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.18224972588431</v>
       </c>
       <c r="E89">
-        <v>-25.44115924770799</v>
+        <v>-29.81614062888836</v>
       </c>
       <c r="F89">
-        <v>2.549643141619734</v>
+        <v>1.318069485360502</v>
       </c>
       <c r="G89">
-        <v>-4.364263540179686</v>
+        <v>-8.55954244318448</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.01679496147807</v>
       </c>
       <c r="E90">
-        <v>-26.06212171753578</v>
+        <v>-29.76807314153395</v>
       </c>
       <c r="F90">
-        <v>2.591365873961986</v>
+        <v>1.569045696603853</v>
       </c>
       <c r="G90">
-        <v>-3.242375936194849</v>
+        <v>-8.549402242197692</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.835501521867625</v>
       </c>
       <c r="E91">
-        <v>-25.91405420290699</v>
+        <v>-31.40120615800116</v>
       </c>
       <c r="F91">
-        <v>2.61964927790582</v>
+        <v>1.006055664430199</v>
       </c>
       <c r="G91">
-        <v>-4.07285276908534</v>
+        <v>-8.425531559754782</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.630544272617279</v>
       </c>
       <c r="E92">
-        <v>-28.87210323793134</v>
+        <v>-35.60440440617456</v>
       </c>
       <c r="F92">
-        <v>2.922445930408265</v>
+        <v>0.640591768853815</v>
       </c>
       <c r="G92">
-        <v>-4.445626817898354</v>
+        <v>-6.90021094471774</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.393112911186851</v>
       </c>
       <c r="E93">
-        <v>-29.85610894048006</v>
+        <v>-36.630758133406</v>
       </c>
       <c r="F93">
-        <v>2.471636123048849</v>
+        <v>0.6870830397074554</v>
       </c>
       <c r="G93">
-        <v>-3.865605997235885</v>
+        <v>-7.090640145227698</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.111828165690705</v>
       </c>
       <c r="E94">
-        <v>-32.71122349707307</v>
+        <v>-37.55097122260867</v>
       </c>
       <c r="F94">
-        <v>2.431305468206268</v>
+        <v>0.8180396818551433</v>
       </c>
       <c r="G94">
-        <v>-4.347343341928472</v>
+        <v>-6.930383256762658</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.790986875337531</v>
       </c>
       <c r="E95">
-        <v>-33.99734860728052</v>
+        <v>-40.12220480060884</v>
       </c>
       <c r="F95">
-        <v>2.300306065998863</v>
+        <v>0.7384537084865648</v>
       </c>
       <c r="G95">
-        <v>-4.160271034595335</v>
+        <v>-7.267913237764591</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.426367967121138</v>
       </c>
       <c r="E96">
-        <v>-35.68687471056525</v>
+        <v>-40.43900325676343</v>
       </c>
       <c r="F96">
-        <v>2.143753568845843</v>
+        <v>0.7608140523066543</v>
       </c>
       <c r="G96">
-        <v>-3.102972174081678</v>
+        <v>-6.178492153883386</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.021855235733454</v>
       </c>
       <c r="E97">
-        <v>-38.55498145908626</v>
+        <v>-41.42580076353788</v>
       </c>
       <c r="F97">
-        <v>1.824817369359155</v>
+        <v>0.5027301689148111</v>
       </c>
       <c r="G97">
-        <v>-4.420658683441171</v>
+        <v>-7.761744005312135</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.573379619066896</v>
       </c>
       <c r="E98">
-        <v>-40.85297597241162</v>
+        <v>-42.53666034422646</v>
       </c>
       <c r="F98">
-        <v>2.109575611484744</v>
+        <v>-0.3355340825098234</v>
       </c>
       <c r="G98">
-        <v>-3.312926972182257</v>
+        <v>-8.666360505554604</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.091694811493986</v>
       </c>
       <c r="E99">
-        <v>-43.63469075805131</v>
+        <v>-44.9916276163167</v>
       </c>
       <c r="F99">
-        <v>2.250270461306469</v>
+        <v>-0.2758109487326864</v>
       </c>
       <c r="G99">
-        <v>-3.684601919876233</v>
+        <v>-9.583510731208754</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.577047061217438</v>
       </c>
       <c r="E100">
-        <v>-44.27517321508916</v>
+        <v>-48.22208247679846</v>
       </c>
       <c r="F100">
-        <v>1.426464653036839</v>
+        <v>-0.4286258999252695</v>
       </c>
       <c r="G100">
-        <v>-3.441018600187738</v>
+        <v>-8.110466940782343</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.063324965825281</v>
       </c>
       <c r="E101">
-        <v>-46.5548523152905</v>
+        <v>-51.76876633782836</v>
       </c>
       <c r="F101">
-        <v>1.295343305473946</v>
+        <v>-0.7118344858126019</v>
       </c>
       <c r="G101">
-        <v>-3.23596672003082</v>
+        <v>-8.189814096267595</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.520164052592093</v>
       </c>
       <c r="E102">
-        <v>-48.65614463526318</v>
+        <v>-48.44919676946815</v>
       </c>
       <c r="F102">
-        <v>1.620779034037598</v>
+        <v>-0.009890096618291001</v>
       </c>
       <c r="G102">
-        <v>-4.744294304814783</v>
+        <v>-8.131028739126757</v>
       </c>
     </row>
   </sheetData>
